--- a/multi/det_gemini_pet.xlsx
+++ b/multi/det_gemini_pet.xlsx
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22">
